--- a/public/mapa-geografico-costa-rica.xlsx
+++ b/public/mapa-geografico-costa-rica.xlsx
@@ -1,34 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\job\singularis\projects\ordenex\public\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDE4EA7-EE36-444A-B441-D618685DB34B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15690"/>
   </bookViews>
   <sheets>
-    <sheet name="Jerarquía (revisar)" sheetId="1" r:id="rId1"/>
-    <sheet name="Cantones oficial vs nuestro" sheetId="2" r:id="rId2"/>
-    <sheet name="Resumen" sheetId="3" r:id="rId3"/>
-    <sheet name="Revisar (gaps y notas)" sheetId="4" r:id="rId4"/>
+    <sheet sheetId="1" name="Jerarquía (revisar)" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Cantones oficial vs nuestro" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Resumen" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Revisar (gaps y notas)" state="visible" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1259" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="346">
   <si>
     <t>Provincia</t>
   </si>
@@ -39,235 +28,673 @@
     <t>Distrito</t>
   </si>
   <si>
+    <t>Zona</t>
+  </si>
+  <si>
     <t>San José</t>
   </si>
   <si>
     <t>Carmen</t>
   </si>
   <si>
+    <t>GAM</t>
+  </si>
+  <si>
+    <t>Merced</t>
+  </si>
+  <si>
+    <t>Hospital</t>
+  </si>
+  <si>
+    <t>Catedral</t>
+  </si>
+  <si>
+    <t>Zapote</t>
+  </si>
+  <si>
+    <t>San Francisco de Dos Rios</t>
+  </si>
+  <si>
+    <t>Uruca</t>
+  </si>
+  <si>
+    <t>Mata Redonda</t>
+  </si>
+  <si>
+    <t>Pavas</t>
+  </si>
+  <si>
+    <t>Hatillo</t>
+  </si>
+  <si>
+    <t>San Sebastian</t>
+  </si>
+  <si>
+    <t>Escazú</t>
+  </si>
+  <si>
+    <t>Escazu</t>
+  </si>
+  <si>
+    <t>San Antonio</t>
+  </si>
+  <si>
+    <t>San Rafael</t>
+  </si>
+  <si>
+    <t>Desamparados</t>
+  </si>
+  <si>
+    <t>San Miguel</t>
+  </si>
+  <si>
+    <t>San Juan de Dios</t>
+  </si>
+  <si>
+    <t>San Rafael Arriba</t>
+  </si>
+  <si>
+    <t>Frailes</t>
+  </si>
+  <si>
+    <t>Patarra</t>
+  </si>
+  <si>
+    <t>San Cristobal</t>
+  </si>
+  <si>
+    <t>Rosario</t>
+  </si>
+  <si>
+    <t>Damas</t>
+  </si>
+  <si>
+    <t>San Rafael Abajo</t>
+  </si>
+  <si>
+    <t>Gravilias</t>
+  </si>
+  <si>
+    <t>Los Guido</t>
+  </si>
+  <si>
+    <t>Aserrí</t>
+  </si>
+  <si>
+    <t>Aserri</t>
+  </si>
+  <si>
+    <t>Tarbaca</t>
+  </si>
+  <si>
+    <t>Vuelta de Jorco</t>
+  </si>
+  <si>
+    <t>San Gabriel</t>
+  </si>
+  <si>
+    <t>Salitrillos</t>
+  </si>
+  <si>
+    <t>Mora</t>
+  </si>
+  <si>
+    <t>Colon</t>
+  </si>
+  <si>
+    <t>Goicoechea</t>
+  </si>
+  <si>
+    <t>Guadalupe</t>
+  </si>
+  <si>
+    <t>Gam</t>
+  </si>
+  <si>
+    <t>San Francisco</t>
+  </si>
+  <si>
+    <t>Calle Blancos</t>
+  </si>
+  <si>
+    <t>Mata de Platano</t>
+  </si>
+  <si>
+    <t>Ipis</t>
+  </si>
+  <si>
+    <t>Rancho Redondo</t>
+  </si>
+  <si>
+    <t>Purral</t>
+  </si>
+  <si>
+    <t>Santa Ana</t>
+  </si>
+  <si>
+    <t>Salitral</t>
+  </si>
+  <si>
+    <t>Pozos</t>
+  </si>
+  <si>
+    <t>Piedades</t>
+  </si>
+  <si>
+    <t>Brasil</t>
+  </si>
+  <si>
+    <t>Alajuelita</t>
+  </si>
+  <si>
+    <t>San Josecito</t>
+  </si>
+  <si>
+    <t>Concepcion</t>
+  </si>
+  <si>
+    <t>San Felipe</t>
+  </si>
+  <si>
+    <t>Vázquez de Coronado</t>
+  </si>
+  <si>
+    <t>San Isidro</t>
+  </si>
+  <si>
+    <t>Dulce Nombre de Jesus</t>
+  </si>
+  <si>
+    <t>Patalillo</t>
+  </si>
+  <si>
+    <t>Cascajal</t>
+  </si>
+  <si>
+    <t>Tibás</t>
+  </si>
+  <si>
+    <t>San Juan</t>
+  </si>
+  <si>
+    <t>Cinco Esquinas</t>
+  </si>
+  <si>
+    <t>Anselmo Llorente</t>
+  </si>
+  <si>
+    <t>Leon XIII</t>
+  </si>
+  <si>
+    <t>Colima</t>
+  </si>
+  <si>
+    <t>Moravia</t>
+  </si>
+  <si>
+    <t>San Vicente</t>
+  </si>
+  <si>
+    <t>San Jeronimo</t>
+  </si>
+  <si>
+    <t>La Trinidad</t>
+  </si>
+  <si>
+    <t>Montes de Oca</t>
+  </si>
+  <si>
+    <t>San Pedro</t>
+  </si>
+  <si>
+    <t>Sabanilla</t>
+  </si>
+  <si>
+    <t>Mercedes</t>
+  </si>
+  <si>
+    <t>Curridabat</t>
+  </si>
+  <si>
+    <t>Granadilla</t>
+  </si>
+  <si>
+    <t>Sanchez</t>
+  </si>
+  <si>
+    <t>Tirrases</t>
+  </si>
+  <si>
+    <t>Pérez Zeledón</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Merced</t>
-  </si>
-  <si>
-    <t>Hospital</t>
-  </si>
-  <si>
-    <t>Catedral</t>
-  </si>
-  <si>
-    <t>Zapote</t>
-  </si>
-  <si>
-    <t>San Francisco de Dos Rios</t>
-  </si>
-  <si>
-    <t>Uruca</t>
-  </si>
-  <si>
-    <t>Mata Redonda</t>
-  </si>
-  <si>
-    <t>Pavas</t>
-  </si>
-  <si>
-    <t>Hatillo</t>
-  </si>
-  <si>
-    <t>San Sebastian</t>
-  </si>
-  <si>
-    <t>Escazú</t>
-  </si>
-  <si>
-    <t>Escazu</t>
-  </si>
-  <si>
-    <t>San Antonio</t>
-  </si>
-  <si>
-    <t>San Rafael</t>
-  </si>
-  <si>
-    <t>Desamparados</t>
-  </si>
-  <si>
-    <t>San Miguel</t>
-  </si>
-  <si>
-    <t>San Juan de Dios</t>
-  </si>
-  <si>
-    <t>San Rafael Arriba</t>
-  </si>
-  <si>
-    <t>Frailes</t>
-  </si>
-  <si>
-    <t>Patarra</t>
-  </si>
-  <si>
-    <t>San Cristobal</t>
-  </si>
-  <si>
-    <t>Rosario</t>
-  </si>
-  <si>
-    <t>Damas</t>
-  </si>
-  <si>
-    <t>San Rafael Abajo</t>
-  </si>
-  <si>
-    <t>Gravilias</t>
-  </si>
-  <si>
-    <t>Los Guido</t>
+    <t>Zona Sur</t>
+  </si>
+  <si>
+    <t>Alajuela</t>
+  </si>
+  <si>
+    <t>San Jose</t>
+  </si>
+  <si>
+    <t>Carrizal</t>
+  </si>
+  <si>
+    <t>Guacima</t>
+  </si>
+  <si>
+    <t>Rio Segundo</t>
+  </si>
+  <si>
+    <t>Tambor</t>
+  </si>
+  <si>
+    <t>Garita</t>
+  </si>
+  <si>
+    <t>San Ramón</t>
+  </si>
+  <si>
+    <t>San Ramon</t>
+  </si>
+  <si>
+    <t>SAN RAMÓN</t>
+  </si>
+  <si>
+    <t>Santiago</t>
+  </si>
+  <si>
+    <t>Piedades Norte</t>
+  </si>
+  <si>
+    <t>Piedades Sur</t>
+  </si>
+  <si>
+    <t>Angeles</t>
+  </si>
+  <si>
+    <t>Alfaro</t>
+  </si>
+  <si>
+    <t>Volio</t>
+  </si>
+  <si>
+    <t>Zapotal</t>
+  </si>
+  <si>
+    <t>Penias Blancas</t>
+  </si>
+  <si>
+    <t>San Lorenzo</t>
+  </si>
+  <si>
+    <t>Grecia</t>
+  </si>
+  <si>
+    <t>San Roque</t>
+  </si>
+  <si>
+    <t>Tacares</t>
+  </si>
+  <si>
+    <t>Rio Cuarto</t>
+  </si>
+  <si>
+    <t>Puente de Piedra</t>
+  </si>
+  <si>
+    <t>Bolivar</t>
+  </si>
+  <si>
+    <t>Orotina</t>
+  </si>
+  <si>
+    <t>San Mateo</t>
+  </si>
+  <si>
+    <t>PUNTARENAS</t>
+  </si>
+  <si>
+    <t>Atenas</t>
+  </si>
+  <si>
+    <t>Jesus</t>
+  </si>
+  <si>
+    <t>Santa Eulalia</t>
+  </si>
+  <si>
+    <t>Escobal</t>
+  </si>
+  <si>
+    <t>Naranjo</t>
+  </si>
+  <si>
+    <t>Cirri Sur</t>
+  </si>
+  <si>
+    <t>El Rosario</t>
+  </si>
+  <si>
+    <t>Palmares</t>
+  </si>
+  <si>
+    <t>Zaragoza</t>
+  </si>
+  <si>
+    <t>Buenos Aires</t>
+  </si>
+  <si>
+    <t>Candelaria</t>
+  </si>
+  <si>
+    <t>Esquipulas</t>
+  </si>
+  <si>
+    <t>La Granja</t>
+  </si>
+  <si>
+    <t>Centro</t>
+  </si>
+  <si>
+    <t>San Carlos</t>
+  </si>
+  <si>
+    <t>Quesada</t>
+  </si>
+  <si>
+    <t>Zarcero</t>
+  </si>
+  <si>
+    <t>Sarchí</t>
+  </si>
+  <si>
+    <t>Río Cuarto</t>
+  </si>
+  <si>
+    <t>Cartago</t>
+  </si>
+  <si>
+    <t>Occidental</t>
+  </si>
+  <si>
+    <t>San Nicolas</t>
+  </si>
+  <si>
+    <t>Aguacaliente</t>
+  </si>
+  <si>
+    <t>Tierra Blanca</t>
+  </si>
+  <si>
+    <t>Dulce Nombre</t>
+  </si>
+  <si>
+    <t>Llano Grande</t>
+  </si>
+  <si>
+    <t>Quebradilla</t>
+  </si>
+  <si>
+    <t>Paraíso</t>
+  </si>
+  <si>
+    <t>Paraiso</t>
+  </si>
+  <si>
+    <t>Llanos de Santa Lucia</t>
+  </si>
+  <si>
+    <t>La Unión</t>
+  </si>
+  <si>
+    <t>Tres Rios</t>
+  </si>
+  <si>
+    <t>San Diego</t>
+  </si>
+  <si>
+    <t>Rio Azul</t>
+  </si>
+  <si>
+    <t>Oreamuno</t>
+  </si>
+  <si>
+    <t>Potrero Cerrado</t>
+  </si>
+  <si>
+    <t>Cipreses</t>
+  </si>
+  <si>
+    <t>Santa Rosa</t>
+  </si>
+  <si>
+    <t>El Guarco</t>
+  </si>
+  <si>
+    <t>El Tejar</t>
+  </si>
+  <si>
+    <t>Tobosi</t>
+  </si>
+  <si>
+    <t>Patio de Agua</t>
+  </si>
+  <si>
+    <t>Heredia</t>
+  </si>
+  <si>
+    <t>Ulloa</t>
+  </si>
+  <si>
+    <t>Vara Blanca</t>
+  </si>
+  <si>
+    <t>Barva</t>
+  </si>
+  <si>
+    <t>San Pablo</t>
+  </si>
+  <si>
+    <t>Santa Lucia</t>
+  </si>
+  <si>
+    <t>San Jose de la Montana</t>
+  </si>
+  <si>
+    <t>Santo Domingo</t>
+  </si>
+  <si>
+    <t>Paracito</t>
+  </si>
+  <si>
+    <t>Santo Tomas</t>
+  </si>
+  <si>
+    <t>Tures</t>
+  </si>
+  <si>
+    <t>Para</t>
+  </si>
+  <si>
+    <t>Santa Bárbara</t>
+  </si>
+  <si>
+    <t>Santa Barbara</t>
+  </si>
+  <si>
+    <t>Puraba</t>
+  </si>
+  <si>
+    <t>Belén</t>
+  </si>
+  <si>
+    <t>La Ribera</t>
+  </si>
+  <si>
+    <t>La Asuncion</t>
+  </si>
+  <si>
+    <t>Flores</t>
+  </si>
+  <si>
+    <t>San Joaquin</t>
+  </si>
+  <si>
+    <t>Barrantes</t>
+  </si>
+  <si>
+    <t>Llorente</t>
+  </si>
+  <si>
+    <t>Rincon de Sabanilla</t>
+  </si>
+  <si>
+    <t>Sarapiquí</t>
+  </si>
+  <si>
+    <t>Puerto Viejo</t>
+  </si>
+  <si>
+    <t>LIMÓN ABAJO</t>
+  </si>
+  <si>
+    <t>La Virgen</t>
+  </si>
+  <si>
+    <t>Las Horquetas</t>
+  </si>
+  <si>
+    <t>Llanuras del Gaspar</t>
+  </si>
+  <si>
+    <t>Cure</t>
+  </si>
+  <si>
+    <t>Guanacaste</t>
+  </si>
+  <si>
+    <t>Liberia</t>
+  </si>
+  <si>
+    <t>GUANACASTE</t>
+  </si>
+  <si>
+    <t>Nicoya</t>
+  </si>
+  <si>
+    <t>Santa Cruz</t>
+  </si>
+  <si>
+    <t>Bagaces</t>
+  </si>
+  <si>
+    <t>Pijije</t>
+  </si>
+  <si>
+    <t>Carrillo</t>
+  </si>
+  <si>
+    <t>Cañas</t>
+  </si>
+  <si>
+    <t>Nandayure</t>
+  </si>
+  <si>
+    <t>La Cruz</t>
+  </si>
+  <si>
+    <t>Hojancha</t>
+  </si>
+  <si>
+    <t>Puntarenas</t>
+  </si>
+  <si>
+    <t>Esparza</t>
+  </si>
+  <si>
+    <t>ZONA SUR</t>
+  </si>
+  <si>
+    <t>Cabagra</t>
+  </si>
+  <si>
+    <t>Montes de Oro</t>
+  </si>
+  <si>
+    <t>Osa</t>
+  </si>
+  <si>
+    <t>Quepos</t>
+  </si>
+  <si>
+    <t>QUEPOS</t>
+  </si>
+  <si>
+    <t>Golfito</t>
+  </si>
+  <si>
+    <t>Coto Brus</t>
+  </si>
+  <si>
+    <t>Parrita</t>
+  </si>
+  <si>
+    <t>Corredores</t>
+  </si>
+  <si>
+    <t>Garabito</t>
+  </si>
+  <si>
+    <t>Puerto Jiménez</t>
+  </si>
+  <si>
+    <t>Limón</t>
+  </si>
+  <si>
+    <t>Pococí</t>
+  </si>
+  <si>
+    <t>LIMON ABAJO</t>
+  </si>
+  <si>
+    <t>Cantón oficial</t>
+  </si>
+  <si>
+    <t>¿Lo tenemos?</t>
+  </si>
+  <si>
+    <t>Distritos mapeados (N)</t>
+  </si>
+  <si>
+    <t>Notas</t>
+  </si>
+  <si>
+    <t>Sí</t>
   </si>
   <si>
     <t>Puriscal</t>
   </si>
   <si>
-    <t>Santiago</t>
-  </si>
-  <si>
     <t>Tarrazú</t>
   </si>
   <si>
-    <t>Aserrí</t>
-  </si>
-  <si>
-    <t>Aserri</t>
-  </si>
-  <si>
-    <t>Tarbaca</t>
-  </si>
-  <si>
-    <t>Vuelta de Jorco</t>
-  </si>
-  <si>
-    <t>San Gabriel</t>
-  </si>
-  <si>
-    <t>Salitrillos</t>
-  </si>
-  <si>
-    <t>Mora</t>
-  </si>
-  <si>
-    <t>Colon</t>
-  </si>
-  <si>
-    <t>Goicoechea</t>
-  </si>
-  <si>
-    <t>Guadalupe</t>
-  </si>
-  <si>
-    <t>San Francisco</t>
-  </si>
-  <si>
-    <t>Calle Blancos</t>
-  </si>
-  <si>
-    <t>Mata de Platano</t>
-  </si>
-  <si>
-    <t>Ipis</t>
-  </si>
-  <si>
-    <t>Rancho Redondo</t>
-  </si>
-  <si>
-    <t>Purral</t>
-  </si>
-  <si>
-    <t>Santa Ana</t>
-  </si>
-  <si>
-    <t>Salitral</t>
-  </si>
-  <si>
-    <t>Pozos</t>
-  </si>
-  <si>
-    <t>Piedades</t>
-  </si>
-  <si>
-    <t>Brasil</t>
-  </si>
-  <si>
-    <t>Alajuelita</t>
-  </si>
-  <si>
-    <t>San Josecito</t>
-  </si>
-  <si>
-    <t>Concepcion</t>
-  </si>
-  <si>
-    <t>San Felipe</t>
-  </si>
-  <si>
-    <t>Vázquez de Coronado</t>
-  </si>
-  <si>
-    <t>San Isidro</t>
-  </si>
-  <si>
-    <t>Dulce Nombre de Jesus</t>
-  </si>
-  <si>
-    <t>Patalillo</t>
-  </si>
-  <si>
-    <t>Cascajal</t>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>⚠ FALTA — no está en el catálogo</t>
   </si>
   <si>
     <t>Acosta</t>
   </si>
   <si>
-    <t>Tibás</t>
-  </si>
-  <si>
-    <t>San Juan</t>
-  </si>
-  <si>
-    <t>Cinco Esquinas</t>
-  </si>
-  <si>
-    <t>Anselmo Llorente</t>
-  </si>
-  <si>
-    <t>Leon XIII</t>
-  </si>
-  <si>
-    <t>Colima</t>
-  </si>
-  <si>
-    <t>Moravia</t>
-  </si>
-  <si>
-    <t>San Vicente</t>
-  </si>
-  <si>
-    <t>San Jeronimo</t>
-  </si>
-  <si>
-    <t>La Trinidad</t>
-  </si>
-  <si>
-    <t>Montes de Oca</t>
-  </si>
-  <si>
-    <t>San Pedro</t>
-  </si>
-  <si>
-    <t>Sabanilla</t>
-  </si>
-  <si>
-    <t>Mercedes</t>
+    <t>Sin distritos mapeados (completar)</t>
   </si>
   <si>
     <t>Turrubares</t>
@@ -276,153 +703,12 @@
     <t>Dota</t>
   </si>
   <si>
-    <t>Curridabat</t>
-  </si>
-  <si>
-    <t>Granadilla</t>
-  </si>
-  <si>
-    <t>Sanchez</t>
-  </si>
-  <si>
-    <t>Tirrases</t>
-  </si>
-  <si>
-    <t>Pérez Zeledón</t>
-  </si>
-  <si>
     <t>León Cortés</t>
   </si>
   <si>
-    <t>Alajuela</t>
-  </si>
-  <si>
-    <t>San Jose</t>
-  </si>
-  <si>
-    <t>Carrizal</t>
-  </si>
-  <si>
-    <t>Guacima</t>
-  </si>
-  <si>
-    <t>Rio Segundo</t>
-  </si>
-  <si>
-    <t>Tambor</t>
-  </si>
-  <si>
-    <t>Garita</t>
-  </si>
-  <si>
-    <t>San Ramón</t>
-  </si>
-  <si>
-    <t>San Ramon</t>
-  </si>
-  <si>
-    <t>Piedades Norte</t>
-  </si>
-  <si>
-    <t>Piedades Sur</t>
-  </si>
-  <si>
-    <t>Angeles</t>
-  </si>
-  <si>
-    <t>Alfaro</t>
-  </si>
-  <si>
-    <t>Volio</t>
-  </si>
-  <si>
-    <t>Zapotal</t>
-  </si>
-  <si>
-    <t>Penias Blancas</t>
-  </si>
-  <si>
-    <t>San Lorenzo</t>
-  </si>
-  <si>
-    <t>Grecia</t>
-  </si>
-  <si>
-    <t>San Roque</t>
-  </si>
-  <si>
-    <t>Tacares</t>
-  </si>
-  <si>
-    <t>Rio Cuarto</t>
-  </si>
-  <si>
-    <t>Puente de Piedra</t>
-  </si>
-  <si>
-    <t>Bolivar</t>
-  </si>
-  <si>
-    <t>San Mateo</t>
-  </si>
-  <si>
-    <t>Atenas</t>
-  </si>
-  <si>
-    <t>Jesus</t>
-  </si>
-  <si>
-    <t>Santa Eulalia</t>
-  </si>
-  <si>
-    <t>Escobal</t>
-  </si>
-  <si>
-    <t>Naranjo</t>
-  </si>
-  <si>
-    <t>Cirri Sur</t>
-  </si>
-  <si>
-    <t>El Rosario</t>
-  </si>
-  <si>
-    <t>Palmares</t>
-  </si>
-  <si>
-    <t>Zaragoza</t>
-  </si>
-  <si>
-    <t>Buenos Aires</t>
-  </si>
-  <si>
-    <t>Candelaria</t>
-  </si>
-  <si>
-    <t>Esquipulas</t>
-  </si>
-  <si>
-    <t>La Granja</t>
-  </si>
-  <si>
     <t>Poás</t>
   </si>
   <si>
-    <t>Orotina</t>
-  </si>
-  <si>
-    <t>San Carlos</t>
-  </si>
-  <si>
-    <t>Quesada</t>
-  </si>
-  <si>
-    <t>Zarcero</t>
-  </si>
-  <si>
-    <t>Sarchí</t>
-  </si>
-  <si>
     <t>Upala</t>
   </si>
   <si>
@@ -432,252 +718,24 @@
     <t>Guatuso</t>
   </si>
   <si>
-    <t>Río Cuarto</t>
-  </si>
-  <si>
-    <t>Cartago</t>
-  </si>
-  <si>
-    <t>Occidental</t>
-  </si>
-  <si>
-    <t>San Nicolas</t>
-  </si>
-  <si>
-    <t>Aguacaliente</t>
-  </si>
-  <si>
-    <t>Tierra Blanca</t>
-  </si>
-  <si>
-    <t>Dulce Nombre</t>
-  </si>
-  <si>
-    <t>Llano Grande</t>
-  </si>
-  <si>
-    <t>Quebradilla</t>
-  </si>
-  <si>
-    <t>Paraíso</t>
-  </si>
-  <si>
-    <t>Paraiso</t>
-  </si>
-  <si>
-    <t>Llanos de Santa Lucia</t>
-  </si>
-  <si>
-    <t>La Unión</t>
-  </si>
-  <si>
-    <t>Tres Rios</t>
-  </si>
-  <si>
-    <t>San Diego</t>
-  </si>
-  <si>
-    <t>Rio Azul</t>
-  </si>
-  <si>
     <t>Jiménez</t>
   </si>
   <si>
     <t>Turrialba</t>
   </si>
   <si>
-    <t>Santa Cruz</t>
-  </si>
-  <si>
-    <t>Santa Rosa</t>
-  </si>
-  <si>
     <t>Alvarado</t>
   </si>
   <si>
-    <t>Oreamuno</t>
-  </si>
-  <si>
-    <t>Potrero Cerrado</t>
-  </si>
-  <si>
-    <t>Cipreses</t>
-  </si>
-  <si>
-    <t>El Guarco</t>
-  </si>
-  <si>
-    <t>El Tejar</t>
-  </si>
-  <si>
-    <t>Tobosi</t>
-  </si>
-  <si>
-    <t>Patio de Agua</t>
-  </si>
-  <si>
-    <t>Heredia</t>
-  </si>
-  <si>
-    <t>Ulloa</t>
-  </si>
-  <si>
-    <t>Vara Blanca</t>
-  </si>
-  <si>
-    <t>Barva</t>
-  </si>
-  <si>
-    <t>San Pablo</t>
-  </si>
-  <si>
-    <t>Santa Lucia</t>
-  </si>
-  <si>
-    <t>San Jose de la Montana</t>
-  </si>
-  <si>
-    <t>Santo Domingo</t>
-  </si>
-  <si>
-    <t>Paracito</t>
-  </si>
-  <si>
-    <t>Santo Tomas</t>
-  </si>
-  <si>
-    <t>Tures</t>
-  </si>
-  <si>
-    <t>Para</t>
-  </si>
-  <si>
-    <t>Santa Bárbara</t>
-  </si>
-  <si>
-    <t>Santa Barbara</t>
-  </si>
-  <si>
-    <t>Puraba</t>
-  </si>
-  <si>
-    <t>Belén</t>
-  </si>
-  <si>
-    <t>La Ribera</t>
-  </si>
-  <si>
-    <t>La Asuncion</t>
-  </si>
-  <si>
-    <t>Flores</t>
-  </si>
-  <si>
-    <t>San Joaquin</t>
-  </si>
-  <si>
-    <t>Barrantes</t>
-  </si>
-  <si>
-    <t>Llorente</t>
-  </si>
-  <si>
-    <t>Rincon de Sabanilla</t>
-  </si>
-  <si>
-    <t>Sarapiquí</t>
-  </si>
-  <si>
-    <t>Puerto Viejo</t>
-  </si>
-  <si>
-    <t>La Virgen</t>
-  </si>
-  <si>
-    <t>Las Horquetas</t>
-  </si>
-  <si>
-    <t>Llanuras del Gaspar</t>
-  </si>
-  <si>
-    <t>Cure</t>
-  </si>
-  <si>
-    <t>Guanacaste</t>
-  </si>
-  <si>
-    <t>Liberia</t>
-  </si>
-  <si>
-    <t>Nicoya</t>
-  </si>
-  <si>
-    <t>Bagaces</t>
-  </si>
-  <si>
-    <t>Carrillo</t>
-  </si>
-  <si>
-    <t>Cañas</t>
-  </si>
-  <si>
     <t>Abangares</t>
   </si>
   <si>
     <t>Tilarán</t>
   </si>
   <si>
-    <t>Nandayure</t>
-  </si>
-  <si>
-    <t>La Cruz</t>
-  </si>
-  <si>
-    <t>Hojancha</t>
-  </si>
-  <si>
-    <t>Puntarenas</t>
-  </si>
-  <si>
-    <t>Esparza</t>
-  </si>
-  <si>
-    <t>Montes de Oro</t>
-  </si>
-  <si>
-    <t>Osa</t>
-  </si>
-  <si>
-    <t>Quepos</t>
-  </si>
-  <si>
-    <t>Golfito</t>
-  </si>
-  <si>
-    <t>Coto Brus</t>
-  </si>
-  <si>
-    <t>Parrita</t>
-  </si>
-  <si>
-    <t>Corredores</t>
-  </si>
-  <si>
-    <t>Garabito</t>
-  </si>
-  <si>
     <t>Monteverde</t>
   </si>
   <si>
-    <t>Puerto Jiménez</t>
-  </si>
-  <si>
-    <t>Limón</t>
-  </si>
-  <si>
-    <t>Pococí</t>
-  </si>
-  <si>
     <t>Siquirres</t>
   </si>
   <si>
@@ -690,33 +748,6 @@
     <t>Guácimo</t>
   </si>
   <si>
-    <t>Cantón oficial</t>
-  </si>
-  <si>
-    <t>¿Lo tenemos?</t>
-  </si>
-  <si>
-    <t>Distritos mapeados (N)</t>
-  </si>
-  <si>
-    <t>Notas</t>
-  </si>
-  <si>
-    <t>Sí</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>⚠ FALTA — no está en el catálogo</t>
-  </si>
-  <si>
-    <t>Sin distritos mapeados (completar)</t>
-  </si>
-  <si>
     <t>Cantones oficiales</t>
   </si>
   <si>
@@ -1024,55 +1055,26 @@
   </si>
   <si>
     <t>→ Curridabat</t>
-  </si>
-  <si>
-    <t>GAM</t>
-  </si>
-  <si>
-    <t>Gam</t>
-  </si>
-  <si>
-    <t>SAN RAMÓN</t>
-  </si>
-  <si>
-    <t>PUNTARENAS</t>
-  </si>
-  <si>
-    <t>Centro</t>
-  </si>
-  <si>
-    <t>GUANACASTE</t>
-  </si>
-  <si>
-    <t>QUEPOS</t>
-  </si>
-  <si>
-    <t>LIMON ABAJO</t>
-  </si>
-  <si>
-    <t>Zona</t>
-  </si>
-  <si>
-    <t>Zona Sur</t>
-  </si>
-  <si>
-    <t>LIMÓN ABAJO</t>
-  </si>
-  <si>
-    <t>ZONA SUR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1095,24 +1097,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1445,9 +1441,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D232"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D234"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.875" customWidth="1"/>
     <col min="2" max="2" width="22.875" customWidth="1"/>
@@ -1466,1608 +1462,1608 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>340</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>332</v>
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="4"/>
+        <v>7</v>
+      </c>
+      <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="4"/>
+        <v>8</v>
+      </c>
+      <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="4"/>
+        <v>9</v>
+      </c>
+      <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="4"/>
+        <v>10</v>
+      </c>
+      <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="4"/>
+        <v>11</v>
+      </c>
+      <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="4"/>
+        <v>12</v>
+      </c>
+      <c r="D8" s="1"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="4"/>
+        <v>13</v>
+      </c>
+      <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="4"/>
+        <v>16</v>
+      </c>
+      <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="4"/>
+        <v>20</v>
+      </c>
+      <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="4"/>
+        <v>21</v>
+      </c>
+      <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="4"/>
+        <v>22</v>
+      </c>
+      <c r="D17" s="1"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="4"/>
+        <v>23</v>
+      </c>
+      <c r="D18" s="1"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="D19" s="1"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D20" s="1"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
-      </c>
-      <c r="D21" s="4"/>
+        <v>25</v>
+      </c>
+      <c r="D21" s="1"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
-      </c>
-      <c r="D22" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="D22" s="1"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>26</v>
-      </c>
-      <c r="D23" s="4"/>
+        <v>27</v>
+      </c>
+      <c r="D23" s="1"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
-      </c>
-      <c r="D24" s="4"/>
+        <v>28</v>
+      </c>
+      <c r="D24" s="1"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C25" t="s">
-        <v>28</v>
-      </c>
-      <c r="D25" s="4"/>
+        <v>29</v>
+      </c>
+      <c r="D25" s="1"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
-      </c>
-      <c r="D26" s="4"/>
+        <v>30</v>
+      </c>
+      <c r="D26" s="1"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C27" t="s">
-        <v>30</v>
-      </c>
-      <c r="D27" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="D27" s="1"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C28" t="s">
-        <v>31</v>
-      </c>
-      <c r="D28" s="4"/>
+        <v>32</v>
+      </c>
+      <c r="D28" s="1"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>36</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>332</v>
+        <v>34</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" t="s">
         <v>35</v>
       </c>
-      <c r="C30" t="s">
-        <v>37</v>
-      </c>
-      <c r="D30" s="4"/>
+      <c r="D30" s="1"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B31" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C31" t="s">
-        <v>38</v>
-      </c>
-      <c r="D31" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="D31" s="1"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C32" t="s">
-        <v>39</v>
-      </c>
-      <c r="D32" s="4"/>
+        <v>37</v>
+      </c>
+      <c r="D32" s="1"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B33" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C33" t="s">
-        <v>40</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>332</v>
+        <v>38</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B34" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C34" t="s">
-        <v>42</v>
-      </c>
-      <c r="D34" s="4"/>
+        <v>40</v>
+      </c>
+      <c r="D34" s="1"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B35" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35" t="s">
+        <v>42</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C35" t="s">
-        <v>44</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B36" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C36" t="s">
-        <v>45</v>
-      </c>
-      <c r="D36" s="4"/>
+        <v>44</v>
+      </c>
+      <c r="D36" s="1"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B37" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>46</v>
-      </c>
-      <c r="D37" s="4"/>
+        <v>45</v>
+      </c>
+      <c r="D37" s="1"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B38" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C38" t="s">
-        <v>47</v>
-      </c>
-      <c r="D38" s="4"/>
+        <v>46</v>
+      </c>
+      <c r="D38" s="1"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C39" t="s">
-        <v>48</v>
-      </c>
-      <c r="D39" s="4"/>
+        <v>47</v>
+      </c>
+      <c r="D39" s="1"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B40" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C40" t="s">
-        <v>49</v>
-      </c>
-      <c r="D40" s="4"/>
+        <v>48</v>
+      </c>
+      <c r="D40" s="1"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B41" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C41" t="s">
-        <v>50</v>
-      </c>
-      <c r="D41" s="4"/>
+        <v>49</v>
+      </c>
+      <c r="D41" s="1"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B42" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C42" t="s">
-        <v>51</v>
-      </c>
-      <c r="D42" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="D42" s="1"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B43" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43" t="s">
         <v>51</v>
       </c>
-      <c r="C43" t="s">
-        <v>52</v>
-      </c>
-      <c r="D43" s="4"/>
+      <c r="D43" s="1"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B44" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C44" t="s">
-        <v>53</v>
-      </c>
-      <c r="D44" s="4"/>
+        <v>52</v>
+      </c>
+      <c r="D44" s="1"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B45" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C45" t="s">
-        <v>11</v>
-      </c>
-      <c r="D45" s="4"/>
+        <v>12</v>
+      </c>
+      <c r="D45" s="1"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>54</v>
-      </c>
-      <c r="D46" s="4"/>
+        <v>53</v>
+      </c>
+      <c r="D46" s="1"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47" t="s">
-        <v>55</v>
-      </c>
-      <c r="D47" s="4"/>
+        <v>54</v>
+      </c>
+      <c r="D47" s="1"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B48" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C48" t="s">
-        <v>56</v>
-      </c>
-      <c r="D48" s="4"/>
+        <v>55</v>
+      </c>
+      <c r="D48" s="1"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B49" t="s">
+        <v>55</v>
+      </c>
+      <c r="C49" t="s">
         <v>56</v>
       </c>
-      <c r="C49" t="s">
-        <v>57</v>
-      </c>
-      <c r="D49" s="4"/>
+      <c r="D49" s="1"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B50" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C50" t="s">
-        <v>18</v>
-      </c>
-      <c r="D50" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D50" s="1"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B51" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>58</v>
-      </c>
-      <c r="D51" s="4"/>
+        <v>57</v>
+      </c>
+      <c r="D51" s="1"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C52" t="s">
-        <v>59</v>
-      </c>
-      <c r="D52" s="4"/>
+        <v>58</v>
+      </c>
+      <c r="D52" s="1"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B53" t="s">
+        <v>59</v>
+      </c>
+      <c r="C53" t="s">
         <v>60</v>
       </c>
-      <c r="C53" t="s">
-        <v>61</v>
-      </c>
-      <c r="D53" s="4"/>
+      <c r="D53" s="1"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C54" t="s">
-        <v>19</v>
-      </c>
-      <c r="D54" s="4"/>
+        <v>20</v>
+      </c>
+      <c r="D54" s="1"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B55" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C55" t="s">
-        <v>62</v>
-      </c>
-      <c r="D55" s="4"/>
+        <v>61</v>
+      </c>
+      <c r="D55" s="1"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56" t="s">
-        <v>63</v>
-      </c>
-      <c r="D56" s="4"/>
+        <v>62</v>
+      </c>
+      <c r="D56" s="1"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B57" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C57" t="s">
-        <v>64</v>
-      </c>
-      <c r="D57" s="4"/>
+        <v>63</v>
+      </c>
+      <c r="D57" s="1"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B58" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C58" t="s">
-        <v>67</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>333</v>
+        <v>65</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B59" t="s">
+        <v>64</v>
+      </c>
+      <c r="C59" t="s">
         <v>66</v>
       </c>
-      <c r="C59" t="s">
-        <v>68</v>
-      </c>
-      <c r="D59" s="4"/>
+      <c r="D59" s="1"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B60" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C60" t="s">
-        <v>69</v>
-      </c>
-      <c r="D60" s="4"/>
+        <v>67</v>
+      </c>
+      <c r="D60" s="1"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B61" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C61" t="s">
-        <v>70</v>
-      </c>
-      <c r="D61" s="4"/>
+        <v>68</v>
+      </c>
+      <c r="D61" s="1"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B62" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C62" t="s">
-        <v>71</v>
-      </c>
-      <c r="D62" s="4"/>
+        <v>69</v>
+      </c>
+      <c r="D62" s="1"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B63" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C63" t="s">
-        <v>73</v>
-      </c>
-      <c r="D63" s="4"/>
+        <v>71</v>
+      </c>
+      <c r="D63" s="1"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B64" t="s">
+        <v>70</v>
+      </c>
+      <c r="C64" t="s">
         <v>72</v>
       </c>
-      <c r="C64" t="s">
-        <v>74</v>
-      </c>
-      <c r="D64" s="4"/>
+      <c r="D64" s="1"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B65" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C65" t="s">
-        <v>75</v>
-      </c>
-      <c r="D65" s="4"/>
+        <v>73</v>
+      </c>
+      <c r="D65" s="1"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B66" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C66" t="s">
-        <v>77</v>
-      </c>
-      <c r="D66" s="4"/>
+        <v>75</v>
+      </c>
+      <c r="D66" s="1"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B67" t="s">
+        <v>74</v>
+      </c>
+      <c r="C67" t="s">
         <v>76</v>
       </c>
-      <c r="C67" t="s">
-        <v>78</v>
-      </c>
-      <c r="D67" s="4"/>
+      <c r="D67" s="1"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B68" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C68" t="s">
-        <v>79</v>
-      </c>
-      <c r="D68" s="4"/>
+        <v>77</v>
+      </c>
+      <c r="D68" s="1"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B69" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C69" t="s">
-        <v>19</v>
-      </c>
-      <c r="D69" s="4"/>
+        <v>20</v>
+      </c>
+      <c r="D69" s="1"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B70" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C70" t="s">
-        <v>82</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>332</v>
+        <v>78</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B71" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C71" t="s">
-        <v>83</v>
-      </c>
-      <c r="D71" s="4"/>
+        <v>79</v>
+      </c>
+      <c r="D71" s="1"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B72" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C72" t="s">
-        <v>84</v>
-      </c>
-      <c r="D72" s="4"/>
+        <v>80</v>
+      </c>
+      <c r="D72" s="1"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B73" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C73" t="s">
-        <v>85</v>
-      </c>
-      <c r="D73" s="4"/>
+        <v>81</v>
+      </c>
+      <c r="D73" s="1"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B74" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C74" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>341</v>
+        <v>84</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B75" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C75" t="s">
-        <v>88</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>332</v>
+        <v>85</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B76" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C76" t="s">
-        <v>89</v>
-      </c>
-      <c r="D76" s="4"/>
+        <v>86</v>
+      </c>
+      <c r="D76" s="1"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B77" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C77" t="s">
-        <v>90</v>
-      </c>
-      <c r="D77" s="4"/>
+        <v>87</v>
+      </c>
+      <c r="D77" s="1"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B78" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C78" t="s">
-        <v>18</v>
-      </c>
-      <c r="D78" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D78" s="1"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>85</v>
+      </c>
+      <c r="B79" t="s">
+        <v>85</v>
+      </c>
+      <c r="C79" t="s">
         <v>88</v>
       </c>
-      <c r="B79" t="s">
-        <v>88</v>
-      </c>
-      <c r="C79" t="s">
-        <v>91</v>
-      </c>
-      <c r="D79" s="4"/>
+      <c r="D79" s="1"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C80" t="s">
-        <v>61</v>
-      </c>
-      <c r="D80" s="4"/>
+        <v>60</v>
+      </c>
+      <c r="D80" s="1"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B81" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C81" t="s">
-        <v>78</v>
-      </c>
-      <c r="D81" s="4"/>
+        <v>76</v>
+      </c>
+      <c r="D81" s="1"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B82" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C82" t="s">
-        <v>19</v>
-      </c>
-      <c r="D82" s="4"/>
+        <v>20</v>
+      </c>
+      <c r="D82" s="1"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B83" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C83" t="s">
-        <v>92</v>
-      </c>
-      <c r="D83" s="4"/>
+        <v>89</v>
+      </c>
+      <c r="D83" s="1"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C84" t="s">
-        <v>20</v>
-      </c>
-      <c r="D84" s="4"/>
+        <v>21</v>
+      </c>
+      <c r="D84" s="1"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B85" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C85" t="s">
-        <v>93</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>332</v>
+        <v>90</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C86" t="s">
-        <v>94</v>
-      </c>
-      <c r="D86" s="4"/>
+        <v>91</v>
+      </c>
+      <c r="D86" s="1"/>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C87" t="s">
-        <v>96</v>
-      </c>
-      <c r="D87" s="4" t="s">
-        <v>334</v>
+        <v>93</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B88" t="s">
+        <v>92</v>
+      </c>
+      <c r="C88" t="s">
         <v>95</v>
       </c>
-      <c r="C88" t="s">
-        <v>33</v>
-      </c>
-      <c r="D88" s="4"/>
+      <c r="D88" s="1"/>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B89" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C89" t="s">
-        <v>67</v>
-      </c>
-      <c r="D89" s="4"/>
+        <v>65</v>
+      </c>
+      <c r="D89" s="1"/>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B90" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C90" t="s">
-        <v>97</v>
-      </c>
-      <c r="D90" s="4"/>
+        <v>96</v>
+      </c>
+      <c r="D90" s="1"/>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B91" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C91" t="s">
-        <v>98</v>
-      </c>
-      <c r="D91" s="4"/>
+        <v>97</v>
+      </c>
+      <c r="D91" s="1"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B92" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C92" t="s">
-        <v>19</v>
-      </c>
-      <c r="D92" s="4"/>
+        <v>20</v>
+      </c>
+      <c r="D92" s="1"/>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B93" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C93" t="s">
-        <v>61</v>
-      </c>
-      <c r="D93" s="4"/>
+        <v>60</v>
+      </c>
+      <c r="D93" s="1"/>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B94" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C94" t="s">
-        <v>99</v>
-      </c>
-      <c r="D94" s="4"/>
+        <v>98</v>
+      </c>
+      <c r="D94" s="1"/>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C95" t="s">
-        <v>100</v>
-      </c>
-      <c r="D95" s="4"/>
+        <v>99</v>
+      </c>
+      <c r="D95" s="1"/>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B96" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C96" t="s">
-        <v>101</v>
-      </c>
-      <c r="D96" s="4"/>
+        <v>100</v>
+      </c>
+      <c r="D96" s="1"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B97" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C97" t="s">
-        <v>58</v>
-      </c>
-      <c r="D97" s="4"/>
+        <v>57</v>
+      </c>
+      <c r="D97" s="1"/>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B98" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C98" t="s">
-        <v>102</v>
-      </c>
-      <c r="D98" s="4"/>
+        <v>101</v>
+      </c>
+      <c r="D98" s="1"/>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B99" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C99" t="s">
-        <v>103</v>
-      </c>
-      <c r="D99" s="4"/>
+        <v>102</v>
+      </c>
+      <c r="D99" s="1"/>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B100" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C100" t="s">
-        <v>104</v>
-      </c>
-      <c r="D100" s="4"/>
+        <v>103</v>
+      </c>
+      <c r="D100" s="1"/>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B101" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C101" t="s">
-        <v>105</v>
-      </c>
-      <c r="D101" s="4"/>
+        <v>104</v>
+      </c>
+      <c r="D101" s="1"/>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B102" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C102" t="s">
-        <v>61</v>
-      </c>
-      <c r="D102" s="4"/>
+        <v>60</v>
+      </c>
+      <c r="D102" s="1"/>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B103" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C103" t="s">
-        <v>89</v>
-      </c>
-      <c r="D103" s="4"/>
+        <v>86</v>
+      </c>
+      <c r="D103" s="1"/>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B104" t="s">
+        <v>104</v>
+      </c>
+      <c r="C104" t="s">
         <v>105</v>
       </c>
-      <c r="C104" t="s">
-        <v>106</v>
-      </c>
-      <c r="D104" s="4"/>
+      <c r="D104" s="1"/>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C105" t="s">
-        <v>107</v>
-      </c>
-      <c r="D105" s="4"/>
+        <v>106</v>
+      </c>
+      <c r="D105" s="1"/>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B106" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C106" t="s">
-        <v>108</v>
-      </c>
-      <c r="D106" s="4"/>
+        <v>107</v>
+      </c>
+      <c r="D106" s="1"/>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B107" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C107" t="s">
-        <v>109</v>
-      </c>
-      <c r="D107" s="4"/>
+        <v>108</v>
+      </c>
+      <c r="D107" s="1"/>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B108" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C108" t="s">
-        <v>110</v>
-      </c>
-      <c r="D108" s="4"/>
+        <v>109</v>
+      </c>
+      <c r="D108" s="1"/>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B109" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="C109" t="s">
         <v>111</v>
       </c>
-      <c r="D109" s="4" t="s">
-        <v>335</v>
+      <c r="D109" s="1" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B110" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C110" t="s">
-        <v>112</v>
-      </c>
-      <c r="D110" s="4"/>
+        <v>113</v>
+      </c>
+      <c r="D110" s="1"/>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B111" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C111" t="s">
-        <v>113</v>
-      </c>
-      <c r="D111" s="4"/>
+        <v>114</v>
+      </c>
+      <c r="D111" s="1"/>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C112" t="s">
-        <v>79</v>
-      </c>
-      <c r="D112" s="4"/>
+        <v>77</v>
+      </c>
+      <c r="D112" s="1"/>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B113" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C113" t="s">
-        <v>61</v>
-      </c>
-      <c r="D113" s="4"/>
+        <v>60</v>
+      </c>
+      <c r="D113" s="1"/>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B114" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C114" t="s">
-        <v>58</v>
-      </c>
-      <c r="D114" s="4"/>
+        <v>57</v>
+      </c>
+      <c r="D114" s="1"/>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B115" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C115" t="s">
-        <v>89</v>
-      </c>
-      <c r="D115" s="4"/>
+        <v>86</v>
+      </c>
+      <c r="D115" s="1"/>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B116" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C116" t="s">
-        <v>114</v>
-      </c>
-      <c r="D116" s="4"/>
+        <v>115</v>
+      </c>
+      <c r="D116" s="1"/>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B117" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C117" t="s">
-        <v>115</v>
-      </c>
-      <c r="D117" s="4"/>
+        <v>116</v>
+      </c>
+      <c r="D117" s="1"/>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B118" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C118" t="s">
-        <v>116</v>
-      </c>
-      <c r="D118" s="4"/>
+        <v>117</v>
+      </c>
+      <c r="D118" s="1"/>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B119" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C119" t="s">
-        <v>21</v>
-      </c>
-      <c r="D119" s="4"/>
+        <v>22</v>
+      </c>
+      <c r="D119" s="1"/>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B120" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C120" t="s">
-        <v>89</v>
-      </c>
-      <c r="D120" s="4"/>
+        <v>86</v>
+      </c>
+      <c r="D120" s="1"/>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B121" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C121" t="s">
-        <v>117</v>
-      </c>
-      <c r="D121" s="4"/>
+        <v>118</v>
+      </c>
+      <c r="D121" s="1"/>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B122" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C122" t="s">
-        <v>74</v>
-      </c>
-      <c r="D122" s="4"/>
+        <v>72</v>
+      </c>
+      <c r="D122" s="1"/>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B123" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C123" t="s">
-        <v>67</v>
-      </c>
-      <c r="D123" s="4"/>
+        <v>65</v>
+      </c>
+      <c r="D123" s="1"/>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B124" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C124" t="s">
-        <v>118</v>
-      </c>
-      <c r="D124" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="D124" s="1"/>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B125" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C125" t="s">
-        <v>119</v>
-      </c>
-      <c r="D125" s="4"/>
+        <v>120</v>
+      </c>
+      <c r="D125" s="1"/>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B126" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C126" t="s">
-        <v>120</v>
-      </c>
-      <c r="D126" s="4"/>
+        <v>121</v>
+      </c>
+      <c r="D126" s="1"/>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B127" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C127" t="s">
-        <v>121</v>
-      </c>
-      <c r="D127" s="4"/>
+        <v>122</v>
+      </c>
+      <c r="D127" s="1"/>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B128" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C128" t="s">
-        <v>33</v>
-      </c>
-      <c r="D128" s="4"/>
+        <v>95</v>
+      </c>
+      <c r="D128" s="1"/>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B129" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C129" t="s">
-        <v>122</v>
-      </c>
-      <c r="D129" s="4"/>
+        <v>123</v>
+      </c>
+      <c r="D129" s="1"/>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B130" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C130" t="s">
-        <v>123</v>
-      </c>
-      <c r="D130" s="4"/>
+        <v>124</v>
+      </c>
+      <c r="D130" s="1"/>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B131" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C131" t="s">
-        <v>124</v>
-      </c>
-      <c r="D131" s="4"/>
+        <v>125</v>
+      </c>
+      <c r="D131" s="1"/>
     </row>
     <row r="132" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B132" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C132" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C132" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="D132" s="3" t="s">
-        <v>335</v>
+      <c r="D132" s="1" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B133" t="s">
         <v>127</v>
@@ -3076,1276 +3072,1301 @@
         <v>128</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>334</v>
+        <v>94</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B134" t="s">
         <v>129</v>
       </c>
       <c r="C134" t="s">
-        <v>5</v>
-      </c>
-      <c r="D134" s="4" t="s">
-        <v>334</v>
+        <v>83</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B135" t="s">
         <v>130</v>
       </c>
       <c r="C135" t="s">
-        <v>5</v>
-      </c>
-      <c r="D135" s="4"/>
+        <v>83</v>
+      </c>
+      <c r="D135" s="1"/>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B136" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C136" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>334</v>
+        <v>94</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B137" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C137" t="s">
-        <v>136</v>
-      </c>
-      <c r="D137" s="4" t="s">
-        <v>332</v>
+        <v>133</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B138" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C138" t="s">
-        <v>4</v>
-      </c>
-      <c r="D138" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="D138" s="1"/>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B139" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C139" t="s">
-        <v>137</v>
-      </c>
-      <c r="D139" s="4"/>
+        <v>134</v>
+      </c>
+      <c r="D139" s="1"/>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>132</v>
+      </c>
+      <c r="B140" t="s">
+        <v>132</v>
+      </c>
+      <c r="C140" t="s">
         <v>135</v>
       </c>
-      <c r="B140" t="s">
-        <v>135</v>
-      </c>
-      <c r="C140" t="s">
-        <v>138</v>
-      </c>
-      <c r="D140" s="4"/>
+      <c r="D140" s="1"/>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B141" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C141" t="s">
-        <v>44</v>
-      </c>
-      <c r="D141" s="4"/>
+        <v>42</v>
+      </c>
+      <c r="D141" s="1"/>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B142" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C142" t="s">
-        <v>139</v>
-      </c>
-      <c r="D142" s="4" t="s">
-        <v>332</v>
+        <v>136</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B143" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C143" t="s">
-        <v>140</v>
-      </c>
-      <c r="D143" s="4"/>
+        <v>137</v>
+      </c>
+      <c r="D143" s="1"/>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B144" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C144" t="s">
-        <v>141</v>
-      </c>
-      <c r="D144" s="4"/>
+        <v>138</v>
+      </c>
+      <c r="D144" s="1"/>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B145" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C145" t="s">
-        <v>142</v>
-      </c>
-      <c r="D145" s="4"/>
+        <v>139</v>
+      </c>
+      <c r="D145" s="1"/>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B146" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C146" t="s">
-        <v>144</v>
-      </c>
-      <c r="D146" s="4"/>
+        <v>141</v>
+      </c>
+      <c r="D146" s="1"/>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B147" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C147" t="s">
-        <v>33</v>
-      </c>
-      <c r="D147" s="4"/>
+        <v>95</v>
+      </c>
+      <c r="D147" s="1"/>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B148" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C148" t="s">
-        <v>145</v>
-      </c>
-      <c r="D148" s="4" t="s">
-        <v>332</v>
+        <v>142</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B149" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C149" t="s">
-        <v>147</v>
-      </c>
-      <c r="D149" s="4"/>
+        <v>144</v>
+      </c>
+      <c r="D149" s="1"/>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B150" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C150" t="s">
-        <v>148</v>
-      </c>
-      <c r="D150" s="4"/>
+        <v>145</v>
+      </c>
+      <c r="D150" s="1"/>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B151" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C151" t="s">
-        <v>67</v>
-      </c>
-      <c r="D151" s="4"/>
+        <v>65</v>
+      </c>
+      <c r="D151" s="1"/>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B152" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C152" t="s">
-        <v>19</v>
-      </c>
-      <c r="D152" s="4"/>
+        <v>20</v>
+      </c>
+      <c r="D152" s="1"/>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B153" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C153" t="s">
-        <v>58</v>
-      </c>
-      <c r="D153" s="4"/>
+        <v>57</v>
+      </c>
+      <c r="D153" s="1"/>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B154" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C154" t="s">
-        <v>140</v>
-      </c>
-      <c r="D154" s="4"/>
+        <v>137</v>
+      </c>
+      <c r="D154" s="1"/>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B155" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C155" t="s">
-        <v>96</v>
-      </c>
-      <c r="D155" s="4"/>
+        <v>93</v>
+      </c>
+      <c r="D155" s="1"/>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B156" t="s">
+        <v>143</v>
+      </c>
+      <c r="C156" t="s">
         <v>146</v>
       </c>
-      <c r="C156" t="s">
-        <v>149</v>
-      </c>
-      <c r="D156" s="4"/>
+      <c r="D156" s="1"/>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B157" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C157" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>332</v>
+        <v>6</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B158" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C158" t="s">
-        <v>156</v>
-      </c>
-      <c r="D158" s="4" t="s">
-        <v>332</v>
+        <v>148</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B159" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C159" t="s">
-        <v>157</v>
-      </c>
-      <c r="D159" s="4"/>
+        <v>149</v>
+      </c>
+      <c r="D159" s="1"/>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B160" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C160" t="s">
-        <v>153</v>
-      </c>
-      <c r="D160" s="4"/>
+        <v>150</v>
+      </c>
+      <c r="D160" s="1"/>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B161" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C161" t="s">
-        <v>159</v>
-      </c>
-      <c r="D161" s="4"/>
+        <v>152</v>
+      </c>
+      <c r="D161" s="1"/>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B162" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C162" t="s">
-        <v>61</v>
-      </c>
-      <c r="D162" s="4"/>
+        <v>60</v>
+      </c>
+      <c r="D162" s="1"/>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B163" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C163" t="s">
-        <v>160</v>
-      </c>
-      <c r="D163" s="4"/>
+        <v>153</v>
+      </c>
+      <c r="D163" s="1"/>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B164" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C164" t="s">
-        <v>161</v>
-      </c>
-      <c r="D164" s="4"/>
+        <v>154</v>
+      </c>
+      <c r="D164" s="1"/>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B165" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C165" t="s">
-        <v>162</v>
-      </c>
-      <c r="D165" s="4"/>
+        <v>155</v>
+      </c>
+      <c r="D165" s="1"/>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B166" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C166" t="s">
-        <v>79</v>
-      </c>
-      <c r="D166" s="4"/>
+        <v>77</v>
+      </c>
+      <c r="D166" s="1"/>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B167" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C167" t="s">
-        <v>45</v>
-      </c>
-      <c r="D167" s="4"/>
+        <v>44</v>
+      </c>
+      <c r="D167" s="1"/>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B168" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C168" t="s">
-        <v>163</v>
-      </c>
-      <c r="D168" s="4"/>
+        <v>156</v>
+      </c>
+      <c r="D168" s="1"/>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B169" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C169" t="s">
-        <v>164</v>
-      </c>
-      <c r="D169" s="4"/>
+        <v>157</v>
+      </c>
+      <c r="D169" s="1"/>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B170" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C170" t="s">
-        <v>165</v>
-      </c>
-      <c r="D170" s="4"/>
+        <v>158</v>
+      </c>
+      <c r="D170" s="1"/>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B171" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C171" t="s">
-        <v>77</v>
-      </c>
-      <c r="D171" s="4"/>
+        <v>75</v>
+      </c>
+      <c r="D171" s="1"/>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B172" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C172" t="s">
-        <v>166</v>
-      </c>
-      <c r="D172" s="4"/>
+        <v>159</v>
+      </c>
+      <c r="D172" s="1"/>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B173" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C173" t="s">
-        <v>106</v>
-      </c>
-      <c r="D173" s="4"/>
+        <v>105</v>
+      </c>
+      <c r="D173" s="1"/>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B174" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C174" t="s">
-        <v>167</v>
-      </c>
-      <c r="D174" s="4"/>
+        <v>160</v>
+      </c>
+      <c r="D174" s="1"/>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B175" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C175" t="s">
-        <v>168</v>
-      </c>
-      <c r="D175" s="4"/>
+        <v>161</v>
+      </c>
+      <c r="D175" s="1"/>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
+        <v>155</v>
+      </c>
+      <c r="B176" t="s">
         <v>162</v>
       </c>
-      <c r="B176" t="s">
-        <v>169</v>
-      </c>
       <c r="C176" t="s">
-        <v>169</v>
-      </c>
-      <c r="D176" s="4"/>
+        <v>162</v>
+      </c>
+      <c r="D176" s="1"/>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
+        <v>155</v>
+      </c>
+      <c r="B177" t="s">
         <v>162</v>
       </c>
-      <c r="B177" t="s">
-        <v>169</v>
-      </c>
       <c r="C177" t="s">
-        <v>73</v>
-      </c>
-      <c r="D177" s="4"/>
+        <v>71</v>
+      </c>
+      <c r="D177" s="1"/>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
+        <v>155</v>
+      </c>
+      <c r="B178" t="s">
         <v>162</v>
       </c>
-      <c r="B178" t="s">
-        <v>169</v>
-      </c>
       <c r="C178" t="s">
-        <v>21</v>
-      </c>
-      <c r="D178" s="4"/>
+        <v>22</v>
+      </c>
+      <c r="D178" s="1"/>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
+        <v>155</v>
+      </c>
+      <c r="B179" t="s">
         <v>162</v>
       </c>
-      <c r="B179" t="s">
-        <v>169</v>
-      </c>
       <c r="C179" t="s">
-        <v>170</v>
-      </c>
-      <c r="D179" s="4"/>
+        <v>163</v>
+      </c>
+      <c r="D179" s="1"/>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
+        <v>155</v>
+      </c>
+      <c r="B180" t="s">
         <v>162</v>
       </c>
-      <c r="B180" t="s">
-        <v>169</v>
-      </c>
       <c r="C180" t="s">
-        <v>171</v>
-      </c>
-      <c r="D180" s="4"/>
+        <v>164</v>
+      </c>
+      <c r="D180" s="1"/>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
+        <v>155</v>
+      </c>
+      <c r="B181" t="s">
         <v>162</v>
       </c>
-      <c r="B181" t="s">
-        <v>169</v>
-      </c>
       <c r="C181" t="s">
-        <v>153</v>
-      </c>
-      <c r="D181" s="4"/>
+        <v>150</v>
+      </c>
+      <c r="D181" s="1"/>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
+        <v>155</v>
+      </c>
+      <c r="B182" t="s">
         <v>162</v>
       </c>
-      <c r="B182" t="s">
-        <v>169</v>
-      </c>
       <c r="C182" t="s">
-        <v>172</v>
-      </c>
-      <c r="D182" s="4"/>
+        <v>165</v>
+      </c>
+      <c r="D182" s="1"/>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
+        <v>155</v>
+      </c>
+      <c r="B183" t="s">
         <v>162</v>
       </c>
-      <c r="B183" t="s">
-        <v>169</v>
-      </c>
       <c r="C183" t="s">
-        <v>173</v>
-      </c>
-      <c r="D183" s="4"/>
+        <v>166</v>
+      </c>
+      <c r="D183" s="1"/>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B184" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C184" t="s">
-        <v>175</v>
-      </c>
-      <c r="D184" s="4"/>
+        <v>168</v>
+      </c>
+      <c r="D184" s="1"/>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B185" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C185" t="s">
-        <v>77</v>
-      </c>
-      <c r="D185" s="4"/>
+        <v>75</v>
+      </c>
+      <c r="D185" s="1"/>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B186" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C186" t="s">
-        <v>67</v>
-      </c>
-      <c r="D186" s="4"/>
+        <v>65</v>
+      </c>
+      <c r="D186" s="1"/>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B187" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C187" t="s">
-        <v>113</v>
-      </c>
-      <c r="D187" s="4"/>
+        <v>114</v>
+      </c>
+      <c r="D187" s="1"/>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
+        <v>155</v>
+      </c>
+      <c r="B188" t="s">
+        <v>167</v>
+      </c>
+      <c r="C188" t="s">
         <v>162</v>
       </c>
-      <c r="B188" t="s">
-        <v>174</v>
-      </c>
-      <c r="C188" t="s">
-        <v>169</v>
-      </c>
-      <c r="D188" s="4"/>
+      <c r="D188" s="1"/>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B189" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C189" t="s">
-        <v>176</v>
-      </c>
-      <c r="D189" s="4"/>
+        <v>169</v>
+      </c>
+      <c r="D189" s="1"/>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B190" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C190" t="s">
-        <v>19</v>
-      </c>
-      <c r="D190" s="4"/>
+        <v>20</v>
+      </c>
+      <c r="D190" s="1"/>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B191" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C191" t="s">
-        <v>57</v>
-      </c>
-      <c r="D191" s="4"/>
+        <v>56</v>
+      </c>
+      <c r="D191" s="1"/>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B192" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C192" t="s">
-        <v>33</v>
-      </c>
-      <c r="D192" s="4"/>
+        <v>95</v>
+      </c>
+      <c r="D192" s="1"/>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B193" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C193" t="s">
-        <v>99</v>
-      </c>
-      <c r="D193" s="4"/>
+        <v>98</v>
+      </c>
+      <c r="D193" s="1"/>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B194" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C194" t="s">
-        <v>58</v>
-      </c>
-      <c r="D194" s="4"/>
+        <v>57</v>
+      </c>
+      <c r="D194" s="1"/>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B195" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C195" t="s">
-        <v>61</v>
-      </c>
-      <c r="D195" s="4"/>
+        <v>60</v>
+      </c>
+      <c r="D195" s="1"/>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B196" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C196" t="s">
-        <v>89</v>
-      </c>
-      <c r="D196" s="4"/>
+        <v>86</v>
+      </c>
+      <c r="D196" s="1"/>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B197" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C197" t="s">
-        <v>58</v>
-      </c>
-      <c r="D197" s="4"/>
+        <v>57</v>
+      </c>
+      <c r="D197" s="1"/>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B198" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C198" t="s">
-        <v>45</v>
-      </c>
-      <c r="D198" s="4"/>
+        <v>44</v>
+      </c>
+      <c r="D198" s="1"/>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B199" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C199" t="s">
-        <v>18</v>
-      </c>
-      <c r="D199" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="D199" s="1"/>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B200" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C200" t="s">
-        <v>178</v>
-      </c>
-      <c r="D200" s="4"/>
+        <v>171</v>
+      </c>
+      <c r="D200" s="1"/>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B201" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C201" t="s">
-        <v>179</v>
-      </c>
-      <c r="D201" s="4"/>
+        <v>172</v>
+      </c>
+      <c r="D201" s="1"/>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B202" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C202" t="s">
-        <v>181</v>
-      </c>
-      <c r="D202" s="4"/>
+        <v>174</v>
+      </c>
+      <c r="D202" s="1"/>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B203" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C203" t="s">
-        <v>182</v>
-      </c>
-      <c r="D203" s="4"/>
+        <v>175</v>
+      </c>
+      <c r="D203" s="1"/>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B204" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C204" t="s">
-        <v>183</v>
-      </c>
-      <c r="D204" s="4"/>
+        <v>176</v>
+      </c>
+      <c r="D204" s="1"/>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B205" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C205" t="s">
-        <v>166</v>
-      </c>
-      <c r="D205" s="4"/>
+        <v>159</v>
+      </c>
+      <c r="D205" s="1"/>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B206" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C206" t="s">
-        <v>184</v>
-      </c>
-      <c r="D206" s="4"/>
+        <v>177</v>
+      </c>
+      <c r="D206" s="1"/>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B207" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C207" t="s">
-        <v>186</v>
-      </c>
-      <c r="D207" s="4" t="s">
-        <v>342</v>
+        <v>179</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B208" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C208" t="s">
-        <v>187</v>
-      </c>
-      <c r="D208" s="4"/>
+        <v>181</v>
+      </c>
+      <c r="D208" s="1"/>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B209" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C209" t="s">
-        <v>188</v>
-      </c>
-      <c r="D209" s="4"/>
+        <v>182</v>
+      </c>
+      <c r="D209" s="1"/>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B210" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C210" t="s">
-        <v>189</v>
-      </c>
-      <c r="D210" s="4"/>
+        <v>183</v>
+      </c>
+      <c r="D210" s="1"/>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B211" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C211" t="s">
-        <v>190</v>
-      </c>
-      <c r="D211" s="4"/>
+        <v>184</v>
+      </c>
+      <c r="D211" s="1"/>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B212" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C212" t="s">
-        <v>5</v>
-      </c>
-      <c r="D212" s="4" t="s">
-        <v>337</v>
+        <v>83</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B213" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C213" t="s">
-        <v>5</v>
-      </c>
-      <c r="D213" s="4"/>
+        <v>83</v>
+      </c>
+      <c r="D213" s="1"/>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B214" t="s">
-        <v>152</v>
+        <v>189</v>
       </c>
       <c r="C214" t="s">
-        <v>5</v>
-      </c>
-      <c r="D214" s="4"/>
+        <v>83</v>
+      </c>
+      <c r="D214" s="1"/>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
+        <v>185</v>
+      </c>
+      <c r="B215" t="s">
+        <v>190</v>
+      </c>
+      <c r="C215" t="s">
         <v>191</v>
       </c>
-      <c r="B215" t="s">
-        <v>195</v>
-      </c>
-      <c r="C215" t="s">
-        <v>5</v>
-      </c>
-      <c r="D215" s="4" t="s">
-        <v>337</v>
+      <c r="D215" s="1" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B216" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C216" t="s">
-        <v>5</v>
-      </c>
-      <c r="D216" s="4"/>
+        <v>83</v>
+      </c>
+      <c r="D216" s="1" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B217" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="C217" t="s">
-        <v>5</v>
-      </c>
-      <c r="D217" s="4" t="s">
-        <v>337</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="D217" s="1"/>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B218" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C218" t="s">
-        <v>5</v>
-      </c>
-      <c r="D218" s="4"/>
+        <v>83</v>
+      </c>
+      <c r="D218" s="1" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B219" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C219" t="s">
-        <v>5</v>
-      </c>
-      <c r="D219" s="4"/>
+        <v>83</v>
+      </c>
+      <c r="D219" s="1"/>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="B220" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C220" t="s">
-        <v>5</v>
-      </c>
-      <c r="D220" s="4" t="s">
-        <v>335</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="D220" s="1"/>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B221" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C221" t="s">
-        <v>5</v>
-      </c>
-      <c r="D221" s="4"/>
+        <v>83</v>
+      </c>
+      <c r="D221" s="1" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B222" t="s">
-        <v>121</v>
+        <v>198</v>
       </c>
       <c r="C222" t="s">
-        <v>5</v>
-      </c>
-      <c r="D222" s="1" t="s">
-        <v>343</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="D222" s="1"/>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B223" t="s">
-        <v>204</v>
+        <v>122</v>
       </c>
       <c r="C223" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>335</v>
+        <v>199</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B224" t="s">
-        <v>205</v>
+        <v>122</v>
       </c>
       <c r="C224" t="s">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>343</v>
+        <v>199</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B225" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C225" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>338</v>
+        <v>112</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
+        <v>197</v>
+      </c>
+      <c r="B226" t="s">
         <v>202</v>
       </c>
-      <c r="B226" t="s">
-        <v>207</v>
-      </c>
       <c r="C226" t="s">
-        <v>5</v>
-      </c>
-      <c r="D226" s="4" t="s">
-        <v>343</v>
+        <v>83</v>
+      </c>
+      <c r="D226" s="1" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B227" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C227" t="s">
-        <v>5</v>
-      </c>
-      <c r="D227" s="4"/>
+        <v>83</v>
+      </c>
+      <c r="D227" s="1" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B228" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C228" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>338</v>
+        <v>199</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B229" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C229" t="s">
-        <v>5</v>
-      </c>
-      <c r="D229" s="1" t="s">
-        <v>343</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="D229" s="1"/>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B230" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C230" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>338</v>
+        <v>204</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B231" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C231" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>343</v>
+        <v>199</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="B232" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C232" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>339</v>
+        <v>204</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>197</v>
+      </c>
+      <c r="B233" t="s">
+        <v>210</v>
+      </c>
+      <c r="C233" t="s">
+        <v>83</v>
+      </c>
+      <c r="D233" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>211</v>
+      </c>
+      <c r="B234" t="s">
+        <v>212</v>
+      </c>
+      <c r="C234" t="s">
+        <v>83</v>
+      </c>
+      <c r="D234" s="1" t="s">
+        <v>213</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="D70:D73"/>
-    <mergeCell ref="D58:D69"/>
-    <mergeCell ref="D75:D84"/>
-    <mergeCell ref="D85:D86"/>
     <mergeCell ref="D2:D28"/>
     <mergeCell ref="D29:D32"/>
     <mergeCell ref="D33:D34"/>
     <mergeCell ref="D35:D57"/>
+    <mergeCell ref="D58:D69"/>
+    <mergeCell ref="D70:D73"/>
+    <mergeCell ref="D75:D84"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="D87:D108"/>
+    <mergeCell ref="D109:D131"/>
+    <mergeCell ref="D134:D135"/>
+    <mergeCell ref="D137:D141"/>
     <mergeCell ref="D142:D147"/>
     <mergeCell ref="D148:D156"/>
     <mergeCell ref="D158:D206"/>
     <mergeCell ref="D207:D211"/>
-    <mergeCell ref="D87:D108"/>
-    <mergeCell ref="D109:D131"/>
-    <mergeCell ref="D134:D135"/>
-    <mergeCell ref="D137:D141"/>
     <mergeCell ref="D212:D214"/>
-    <mergeCell ref="D215:D216"/>
-    <mergeCell ref="D217:D219"/>
-    <mergeCell ref="D226:D227"/>
-    <mergeCell ref="D220:D221"/>
+    <mergeCell ref="D216:D217"/>
+    <mergeCell ref="D218:D220"/>
+    <mergeCell ref="D221:D222"/>
+    <mergeCell ref="D228:D229"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:C1 A3:C28 A2:C2 A30:C32 A29:C29 A35:C35 A34:C34 A33:C33 A36:C36 A37:C41 A42:C57 A71:C73 A70:C70 A59:C69 A58:C58 A74:C74 A76:C84 A75:C75 A88:C100 A87:C87 A101:C108 A109 A110:C131 A132:B132 A133:C133 A134:C134 A135:C135 A136 A138:C141 A137:C137 A143:C147 A142:C142 A148:C148 A149:C156 A157:C157 A161:C161 A159:C160 A212:C212 A162:C183 A158:C158 A184:C198 A199:C211 A213:C214 A216:C216 A215:C215 A220:C220 A218:C219 A217:C217 A221:C230 A232:C232 A85:C86 A231:C231" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E85"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.875" customWidth="1"/>
     <col min="2" max="2" width="22.875" customWidth="1"/>
@@ -4359,1458 +4380,1455 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C1" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D1" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="E1" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D2">
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D3">
         <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D4">
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>219</v>
       </c>
       <c r="C5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D5">
         <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>220</v>
       </c>
       <c r="C6" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D6" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E6" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D7">
         <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D8">
         <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D9">
         <v>7</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D10">
         <v>6</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D11">
         <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D12">
         <v>5</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>224</v>
       </c>
       <c r="C13" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D14">
         <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D15">
         <v>3</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D16">
         <v>4</v>
       </c>
       <c r="E16" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>226</v>
       </c>
       <c r="C17" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>227</v>
       </c>
       <c r="C18" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D19">
         <v>4</v>
       </c>
       <c r="E19" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>228</v>
       </c>
       <c r="C21" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D22">
         <v>14</v>
       </c>
       <c r="E22" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D23">
         <v>14</v>
       </c>
       <c r="E23" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C24" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D24">
         <v>8</v>
       </c>
       <c r="E24" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B25" t="s">
         <v>111</v>
       </c>
       <c r="C25" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C26" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D26">
         <v>8</v>
       </c>
       <c r="E26" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B27" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C27" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D27">
         <v>7</v>
       </c>
       <c r="E27" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B28" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C28" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D28">
         <v>7</v>
       </c>
       <c r="E28" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B29" t="s">
-        <v>125</v>
+        <v>229</v>
       </c>
       <c r="C29" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D29">
         <v>5</v>
       </c>
       <c r="E29" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B30" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="C30" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B31" t="s">
         <v>127</v>
       </c>
       <c r="C31" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D31">
         <v>13</v>
       </c>
       <c r="E31" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B32" t="s">
         <v>129</v>
       </c>
       <c r="C32" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B33" t="s">
         <v>130</v>
       </c>
       <c r="C33" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B34" t="s">
-        <v>131</v>
+        <v>230</v>
       </c>
       <c r="C34" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B35" t="s">
-        <v>132</v>
+        <v>231</v>
       </c>
       <c r="C35" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B36" t="s">
-        <v>133</v>
+        <v>232</v>
       </c>
       <c r="C36" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B37" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C37" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B38" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C38" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D38">
         <v>11</v>
       </c>
       <c r="E38" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B39" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C39" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D39">
         <v>5</v>
       </c>
       <c r="E39" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B40" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C40" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D40">
         <v>8</v>
       </c>
       <c r="E40" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B41" t="s">
-        <v>150</v>
+        <v>233</v>
       </c>
       <c r="C41" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D41">
         <v>3</v>
       </c>
       <c r="E41" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B42" t="s">
-        <v>151</v>
+        <v>234</v>
       </c>
       <c r="C42" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D42">
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B43" t="s">
-        <v>154</v>
+        <v>235</v>
       </c>
       <c r="C43" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D43">
         <v>3</v>
       </c>
       <c r="E43" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B44" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C44" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D44">
         <v>5</v>
       </c>
       <c r="E44" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B45" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C45" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D45">
         <v>4</v>
       </c>
       <c r="E45" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B46" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C46" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D46">
         <v>5</v>
       </c>
       <c r="E46" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B47" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C47" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D47">
         <v>6</v>
       </c>
       <c r="E47" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>155</v>
+      </c>
+      <c r="B48" t="s">
         <v>162</v>
       </c>
-      <c r="B48" t="s">
-        <v>169</v>
-      </c>
       <c r="C48" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D48">
         <v>8</v>
       </c>
       <c r="E48" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B49" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C49" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D49">
         <v>6</v>
       </c>
       <c r="E49" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B50" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C50" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D50">
         <v>5</v>
       </c>
       <c r="E50" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D51">
         <v>4</v>
       </c>
       <c r="E51" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B52" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C52" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D52">
         <v>3</v>
       </c>
       <c r="E52" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B53" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C53" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D53">
         <v>3</v>
       </c>
       <c r="E53" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B54" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C54" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D54">
         <v>2</v>
       </c>
       <c r="E54" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B55" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C55" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D55">
         <v>5</v>
       </c>
       <c r="E55" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B56" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C56" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B57" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C57" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B58" t="s">
-        <v>152</v>
+        <v>189</v>
       </c>
       <c r="C58" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B59" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C59" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B60" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C60" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B61" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C61" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B62" t="s">
-        <v>197</v>
+        <v>236</v>
       </c>
       <c r="C62" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B63" t="s">
-        <v>198</v>
+        <v>237</v>
       </c>
       <c r="C63" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B64" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C64" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B65" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C65" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B66" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C66" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B67" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C67" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B68" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C68" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B69" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C69" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B70" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C70" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>197</v>
+      </c>
+      <c r="B71" t="s">
         <v>202</v>
       </c>
-      <c r="B71" t="s">
-        <v>205</v>
-      </c>
       <c r="C71" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D71">
         <v>0</v>
       </c>
       <c r="E71" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B72" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C72" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
       <c r="E72" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B73" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C73" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
       <c r="E73" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B74" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C74" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D74">
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B75" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C75" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D75">
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B76" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C76" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D76">
         <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B77" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C77" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D77">
         <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B78" t="s">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="C78" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D78">
         <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B79" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C79" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D79" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E79" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B80" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C80" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D80">
         <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B81" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C81" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D81">
         <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B82" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="C82" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D82">
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B83" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="C83" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D83">
         <v>0</v>
       </c>
       <c r="E83" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B84" t="s">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="C84" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D84">
         <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B85" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="C85" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D85">
         <v>0</v>
       </c>
       <c r="E85" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:E85" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16.875" customWidth="1"/>
     <col min="2" max="3" width="18.875" customWidth="1"/>
@@ -5824,24 +5842,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="C1" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D1" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="E1" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="F1" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>20</v>
@@ -5850,7 +5868,7 @@
         <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>220</v>
       </c>
       <c r="E2">
         <v>89</v>
@@ -5861,7 +5879,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B3">
         <v>16</v>
@@ -5870,7 +5888,7 @@
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E3">
         <v>76</v>
@@ -5881,7 +5899,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B4">
         <v>8</v>
@@ -5890,7 +5908,7 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E4">
         <v>51</v>
@@ -5901,7 +5919,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B5">
         <v>10</v>
@@ -5910,7 +5928,7 @@
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E5">
         <v>47</v>
@@ -5921,7 +5939,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B6">
         <v>11</v>
@@ -5930,7 +5948,7 @@
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -5941,7 +5959,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B7">
         <v>13</v>
@@ -5950,7 +5968,7 @@
         <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -5961,7 +5979,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B8">
         <v>6</v>
@@ -5970,7 +5988,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -5981,7 +5999,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="B10">
         <v>84</v>
@@ -5990,67 +6008,64 @@
         <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="E10">
         <v>263</v>
       </c>
       <c r="F10" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="B12" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="C12" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D12" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="E12" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="F12" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="B13" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="D13" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="E13">
         <v>263</v>
       </c>
       <c r="F13" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:F13" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B77"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40.875" customWidth="1"/>
     <col min="2" max="2" width="60.875" customWidth="1"/>
@@ -6058,608 +6073,605 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="B1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="B2" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="B3" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="B4" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="B5" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="B6" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="B8" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="B9" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="B10" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="B11" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="B12" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="B13" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="B14" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="B15" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="B16" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="B17" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="B18" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="B19" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="B20" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="B21" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="B22" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>283</v>
+      </c>
+      <c r="B23" t="s">
         <v>269</v>
-      </c>
-      <c r="B23" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="B24" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="B25" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="B26" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="B27" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="B28" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="B29" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="B30" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="B31" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="B32" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="B33" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="B34" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="B35" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="B36" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="B37" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="B38" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="B39" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="B40" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="B41" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="B42" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="B43" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="B44" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="B45" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="B46" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="B47" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="B48" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="B49" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="B50" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="B52" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="B53" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="B54" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="B55" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="B56" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="B57" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="B58" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="B59" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="B60" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="B61" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="B62" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="B63" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="B64" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="B65" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="B66" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="B67" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="B68" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="B69" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="B70" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="B71" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="B72" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="B73" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="B74" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="B75" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="B76" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="B77" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:B77" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
--- a/public/mapa-geografico-costa-rica.xlsx
+++ b/public/mapa-geografico-costa-rica.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="345">
   <si>
     <t>Provincia</t>
   </si>
@@ -617,9 +617,6 @@
   </si>
   <si>
     <t>ZONA SUR</t>
-  </si>
-  <si>
-    <t>Cabagra</t>
   </si>
   <si>
     <t>Montes de Oro</t>
@@ -1442,7 +1439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D234"/>
+  <dimension ref="A1:D233"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.875" customWidth="1"/>
@@ -4188,13 +4185,13 @@
         <v>197</v>
       </c>
       <c r="B224" t="s">
-        <v>122</v>
+        <v>200</v>
       </c>
       <c r="C224" t="s">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>199</v>
+        <v>112</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
@@ -4208,7 +4205,7 @@
         <v>83</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>112</v>
+        <v>199</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
@@ -4222,7 +4219,7 @@
         <v>83</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
@@ -4230,13 +4227,13 @@
         <v>197</v>
       </c>
       <c r="B227" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C227" t="s">
         <v>83</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
@@ -4263,7 +4260,9 @@
       <c r="C229" t="s">
         <v>83</v>
       </c>
-      <c r="D229" s="1"/>
+      <c r="D229" s="1" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
@@ -4276,7 +4275,7 @@
         <v>83</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
@@ -4290,7 +4289,7 @@
         <v>83</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
@@ -4304,39 +4303,25 @@
         <v>83</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="B233" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C233" t="s">
         <v>83</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A234" t="s">
-        <v>211</v>
-      </c>
-      <c r="B234" t="s">
         <v>212</v>
       </c>
-      <c r="C234" t="s">
-        <v>83</v>
-      </c>
-      <c r="D234" s="1" t="s">
-        <v>213</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="20">
     <mergeCell ref="D2:D28"/>
     <mergeCell ref="D29:D32"/>
     <mergeCell ref="D33:D34"/>
@@ -4357,7 +4342,6 @@
     <mergeCell ref="D216:D217"/>
     <mergeCell ref="D218:D220"/>
     <mergeCell ref="D221:D222"/>
-    <mergeCell ref="D228:D229"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4380,16 +4364,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C1" t="s">
         <v>214</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>215</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>216</v>
-      </c>
-      <c r="E1" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -4400,7 +4384,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D2">
         <v>11</v>
@@ -4417,7 +4401,7 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D3">
         <v>3</v>
@@ -4434,7 +4418,7 @@
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D4">
         <v>13</v>
@@ -4448,10 +4432,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D5">
         <v>9</v>
@@ -4465,16 +4449,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C6" t="s">
         <v>220</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>221</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>222</v>
-      </c>
-      <c r="E6" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -4485,7 +4469,7 @@
         <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D7">
         <v>7</v>
@@ -4502,7 +4486,7 @@
         <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -4519,7 +4503,7 @@
         <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D9">
         <v>7</v>
@@ -4536,7 +4520,7 @@
         <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D10">
         <v>6</v>
@@ -4553,7 +4537,7 @@
         <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D11">
         <v>5</v>
@@ -4570,7 +4554,7 @@
         <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D12">
         <v>5</v>
@@ -4584,16 +4568,16 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -4604,7 +4588,7 @@
         <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D14">
         <v>5</v>
@@ -4621,7 +4605,7 @@
         <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D15">
         <v>3</v>
@@ -4638,7 +4622,7 @@
         <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D16">
         <v>4</v>
@@ -4652,16 +4636,16 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C17" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -4669,16 +4653,16 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C18" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -4689,7 +4673,7 @@
         <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D19">
         <v>4</v>
@@ -4706,13 +4690,13 @@
         <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -4720,16 +4704,16 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C21" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -4740,7 +4724,7 @@
         <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D22">
         <v>14</v>
@@ -4757,7 +4741,7 @@
         <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D23">
         <v>14</v>
@@ -4774,7 +4758,7 @@
         <v>104</v>
       </c>
       <c r="C24" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D24">
         <v>8</v>
@@ -4791,13 +4775,13 @@
         <v>111</v>
       </c>
       <c r="C25" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -4808,7 +4792,7 @@
         <v>113</v>
       </c>
       <c r="C26" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D26">
         <v>8</v>
@@ -4825,7 +4809,7 @@
         <v>117</v>
       </c>
       <c r="C27" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D27">
         <v>7</v>
@@ -4842,7 +4826,7 @@
         <v>120</v>
       </c>
       <c r="C28" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D28">
         <v>7</v>
@@ -4856,10 +4840,10 @@
         <v>85</v>
       </c>
       <c r="B29" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C29" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D29">
         <v>5</v>
@@ -4876,13 +4860,13 @@
         <v>110</v>
       </c>
       <c r="C30" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -4893,7 +4877,7 @@
         <v>127</v>
       </c>
       <c r="C31" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D31">
         <v>13</v>
@@ -4910,13 +4894,13 @@
         <v>129</v>
       </c>
       <c r="C32" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -4927,13 +4911,13 @@
         <v>130</v>
       </c>
       <c r="C33" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -4941,16 +4925,16 @@
         <v>85</v>
       </c>
       <c r="B34" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C34" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -4958,16 +4942,16 @@
         <v>85</v>
       </c>
       <c r="B35" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C35" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -4975,16 +4959,16 @@
         <v>85</v>
       </c>
       <c r="B36" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C36" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -4995,13 +4979,13 @@
         <v>131</v>
       </c>
       <c r="C37" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -5012,7 +4996,7 @@
         <v>132</v>
       </c>
       <c r="C38" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D38">
         <v>11</v>
@@ -5029,7 +5013,7 @@
         <v>140</v>
       </c>
       <c r="C39" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D39">
         <v>5</v>
@@ -5046,7 +5030,7 @@
         <v>143</v>
       </c>
       <c r="C40" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D40">
         <v>8</v>
@@ -5060,10 +5044,10 @@
         <v>132</v>
       </c>
       <c r="B41" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C41" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D41">
         <v>3</v>
@@ -5077,10 +5061,10 @@
         <v>132</v>
       </c>
       <c r="B42" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C42" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D42">
         <v>12</v>
@@ -5094,10 +5078,10 @@
         <v>132</v>
       </c>
       <c r="B43" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C43" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D43">
         <v>3</v>
@@ -5114,7 +5098,7 @@
         <v>147</v>
       </c>
       <c r="C44" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D44">
         <v>5</v>
@@ -5131,7 +5115,7 @@
         <v>151</v>
       </c>
       <c r="C45" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D45">
         <v>4</v>
@@ -5148,7 +5132,7 @@
         <v>155</v>
       </c>
       <c r="C46" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D46">
         <v>5</v>
@@ -5165,7 +5149,7 @@
         <v>158</v>
       </c>
       <c r="C47" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D47">
         <v>6</v>
@@ -5182,7 +5166,7 @@
         <v>162</v>
       </c>
       <c r="C48" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D48">
         <v>8</v>
@@ -5199,7 +5183,7 @@
         <v>167</v>
       </c>
       <c r="C49" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D49">
         <v>6</v>
@@ -5216,7 +5200,7 @@
         <v>20</v>
       </c>
       <c r="C50" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D50">
         <v>5</v>
@@ -5233,7 +5217,7 @@
         <v>60</v>
       </c>
       <c r="C51" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D51">
         <v>4</v>
@@ -5250,7 +5234,7 @@
         <v>170</v>
       </c>
       <c r="C52" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D52">
         <v>3</v>
@@ -5267,7 +5251,7 @@
         <v>173</v>
       </c>
       <c r="C53" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D53">
         <v>3</v>
@@ -5284,7 +5268,7 @@
         <v>159</v>
       </c>
       <c r="C54" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D54">
         <v>2</v>
@@ -5301,7 +5285,7 @@
         <v>178</v>
       </c>
       <c r="C55" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D55">
         <v>5</v>
@@ -5318,13 +5302,13 @@
         <v>186</v>
       </c>
       <c r="C56" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -5335,13 +5319,13 @@
         <v>188</v>
       </c>
       <c r="C57" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -5352,13 +5336,13 @@
         <v>189</v>
       </c>
       <c r="C58" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -5369,13 +5353,13 @@
         <v>190</v>
       </c>
       <c r="C59" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -5386,13 +5370,13 @@
         <v>192</v>
       </c>
       <c r="C60" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -5403,13 +5387,13 @@
         <v>193</v>
       </c>
       <c r="C61" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -5417,16 +5401,16 @@
         <v>185</v>
       </c>
       <c r="B62" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C62" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -5434,16 +5418,16 @@
         <v>185</v>
       </c>
       <c r="B63" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C63" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -5454,13 +5438,13 @@
         <v>194</v>
       </c>
       <c r="C64" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -5471,13 +5455,13 @@
         <v>195</v>
       </c>
       <c r="C65" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -5488,13 +5472,13 @@
         <v>196</v>
       </c>
       <c r="C66" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -5505,13 +5489,13 @@
         <v>197</v>
       </c>
       <c r="C67" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -5522,13 +5506,13 @@
         <v>198</v>
       </c>
       <c r="C68" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -5539,13 +5523,13 @@
         <v>122</v>
       </c>
       <c r="C69" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -5553,16 +5537,16 @@
         <v>197</v>
       </c>
       <c r="B70" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C70" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -5570,16 +5554,16 @@
         <v>197</v>
       </c>
       <c r="B71" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C71" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D71">
         <v>0</v>
       </c>
       <c r="E71" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -5587,16 +5571,16 @@
         <v>197</v>
       </c>
       <c r="B72" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C72" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
       <c r="E72" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -5604,16 +5588,16 @@
         <v>197</v>
       </c>
       <c r="B73" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C73" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
       <c r="E73" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -5621,16 +5605,16 @@
         <v>197</v>
       </c>
       <c r="B74" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C74" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D74">
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -5638,16 +5622,16 @@
         <v>197</v>
       </c>
       <c r="B75" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C75" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D75">
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -5655,16 +5639,16 @@
         <v>197</v>
       </c>
       <c r="B76" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C76" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D76">
         <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -5672,16 +5656,16 @@
         <v>197</v>
       </c>
       <c r="B77" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C77" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D77">
         <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -5689,16 +5673,16 @@
         <v>197</v>
       </c>
       <c r="B78" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C78" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D78">
         <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -5706,118 +5690,118 @@
         <v>197</v>
       </c>
       <c r="B79" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C79" t="s">
+        <v>220</v>
+      </c>
+      <c r="D79" t="s">
         <v>221</v>
       </c>
-      <c r="D79" t="s">
+      <c r="E79" t="s">
         <v>222</v>
-      </c>
-      <c r="E79" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B80" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C80" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D80">
         <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>210</v>
+      </c>
+      <c r="B81" t="s">
         <v>211</v>
       </c>
-      <c r="B81" t="s">
-        <v>212</v>
-      </c>
       <c r="C81" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D81">
         <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B82" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C82" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D82">
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B83" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C83" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D83">
         <v>0</v>
       </c>
       <c r="E83" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B84" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C84" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D84">
         <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B85" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C85" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D85">
         <v>0</v>
       </c>
       <c r="E85" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -5842,19 +5826,19 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C1" t="s">
         <v>243</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>244</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>245</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>246</v>
-      </c>
-      <c r="F1" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -5868,7 +5852,7 @@
         <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E2">
         <v>89</v>
@@ -5888,7 +5872,7 @@
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E3">
         <v>76</v>
@@ -5908,7 +5892,7 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E4">
         <v>51</v>
@@ -5928,7 +5912,7 @@
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E5">
         <v>47</v>
@@ -5948,7 +5932,7 @@
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -5968,7 +5952,7 @@
         <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -5979,7 +5963,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B8">
         <v>6</v>
@@ -5988,7 +5972,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -5999,7 +5983,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B10">
         <v>84</v>
@@ -6008,7 +5992,7 @@
         <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E10">
         <v>263</v>
@@ -6019,19 +6003,19 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>249</v>
+      </c>
+      <c r="B12" t="s">
         <v>250</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>251</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" t="s">
         <v>252</v>
-      </c>
-      <c r="D12" t="s">
-        <v>83</v>
-      </c>
-      <c r="E12" t="s">
-        <v>253</v>
       </c>
       <c r="F12" t="s">
         <v>83</v>
@@ -6039,7 +6023,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B13" t="s">
         <v>83</v>
@@ -6054,7 +6038,7 @@
         <v>263</v>
       </c>
       <c r="F13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -6073,602 +6057,602 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B1" t="s">
         <v>256</v>
-      </c>
-      <c r="B1" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B2" t="s">
         <v>258</v>
-      </c>
-      <c r="B2" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B4" t="s">
         <v>261</v>
-      </c>
-      <c r="B4" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>263</v>
+      </c>
+      <c r="B6" t="s">
         <v>264</v>
-      </c>
-      <c r="B6" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>265</v>
+      </c>
+      <c r="B8" t="s">
         <v>266</v>
-      </c>
-      <c r="B8" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>267</v>
+      </c>
+      <c r="B9" t="s">
         <v>268</v>
-      </c>
-      <c r="B9" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B12" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B14" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B15" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B16" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B17" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B18" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B19" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B20" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B21" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B22" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B24" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B25" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B26" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B27" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B28" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B29" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B30" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B31" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B32" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B33" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B34" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B35" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B36" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B37" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B38" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B39" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B40" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B41" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B42" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B43" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B44" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B45" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B46" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B47" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B48" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B49" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B50" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>310</v>
+      </c>
+      <c r="B52" t="s">
         <v>311</v>
-      </c>
-      <c r="B52" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>312</v>
+      </c>
+      <c r="B53" t="s">
         <v>313</v>
-      </c>
-      <c r="B53" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B54" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B55" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B56" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B57" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B58" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B59" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B60" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B61" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B62" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>323</v>
+      </c>
+      <c r="B63" t="s">
         <v>324</v>
-      </c>
-      <c r="B63" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B64" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B65" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B66" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>328</v>
+      </c>
+      <c r="B67" t="s">
         <v>329</v>
-      </c>
-      <c r="B67" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B68" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B69" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B70" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B71" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B72" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>335</v>
+      </c>
+      <c r="B73" t="s">
         <v>336</v>
-      </c>
-      <c r="B73" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>337</v>
+      </c>
+      <c r="B74" t="s">
         <v>338</v>
-      </c>
-      <c r="B74" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>339</v>
+      </c>
+      <c r="B75" t="s">
         <v>340</v>
-      </c>
-      <c r="B75" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>341</v>
+      </c>
+      <c r="B76" t="s">
         <v>342</v>
-      </c>
-      <c r="B76" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>343</v>
+      </c>
+      <c r="B77" t="s">
         <v>344</v>
-      </c>
-      <c r="B77" t="s">
-        <v>345</v>
       </c>
     </row>
   </sheetData>
